--- a/templates/樓層巡查剔格表範本.xlsx
+++ b/templates/樓層巡查剔格表範本.xlsx
@@ -105,7 +105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -300,11 +300,88 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -374,6 +451,42 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -743,24 +856,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.5" customWidth="1" min="1" max="1"/>
-    <col width="5.4" customWidth="1" min="2" max="2"/>
-    <col width="5.4" customWidth="1" min="3" max="3"/>
-    <col width="5.4" customWidth="1" min="4" max="4"/>
-    <col width="5.4" customWidth="1" min="5" max="5"/>
-    <col width="5.4" customWidth="1" min="6" max="6"/>
-    <col width="5.4" customWidth="1" min="7" max="7"/>
-    <col width="5.4" customWidth="1" min="8" max="8"/>
-    <col width="5.4" customWidth="1" min="9" max="9"/>
-    <col width="5.4" customWidth="1" min="10" max="10"/>
-    <col width="5.4" customWidth="1" min="11" max="11"/>
-    <col width="5.4" customWidth="1" min="12" max="12"/>
-    <col width="5.4" customWidth="1" min="13" max="13"/>
-    <col width="5.4" customWidth="1" min="14" max="14"/>
-    <col width="5.4" customWidth="1" min="15" max="15"/>
-    <col width="5.4" customWidth="1" min="16" max="16"/>
-    <col width="5.4" customWidth="1" min="17" max="17"/>
-    <col width="5.4" customWidth="1" min="18" max="18"/>
-    <col width="5.4" customWidth="1" min="19" max="19"/>
+    <col width="9.5" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="9.5" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="9.5" customWidth="1" min="16" max="16"/>
+    <col width="9.5" customWidth="1" min="17" max="17"/>
+    <col width="9.5" customWidth="1" min="18" max="18"/>
+    <col width="9.5" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -799,6 +912,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -810,46 +924,46 @@
           <t>善雅樓</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="32" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>善翠樓</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="7" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>善美樓</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="7" t="n"/>
+      <c r="I5" s="31" t="n"/>
+      <c r="J5" s="32" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
           <t>善景樓</t>
         </is>
       </c>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="7" t="n"/>
+      <c r="L5" s="31" t="n"/>
+      <c r="M5" s="32" t="n"/>
       <c r="N5" s="5" t="inlineStr">
         <is>
           <t>善群樓</t>
         </is>
       </c>
-      <c r="O5" s="6" t="n"/>
-      <c r="P5" s="7" t="n"/>
+      <c r="O5" s="31" t="n"/>
+      <c r="P5" s="32" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>善鄰樓</t>
         </is>
       </c>
-      <c r="R5" s="6" t="n"/>
-      <c r="S5" s="7" t="n"/>
+      <c r="R5" s="31" t="n"/>
+      <c r="S5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n"/>
+      <c r="A6" s="33" t="n"/>
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>A翼</t>
@@ -947,36 +1061,36 @@
           <t>2 樓</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="14" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="35" t="n"/>
+      <c r="J7" s="36" t="n"/>
+      <c r="K7" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M7" s="18" t="inlineStr">
+      <c r="M7" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="14" t="n"/>
-      <c r="P7" s="15" t="n"/>
-      <c r="Q7" s="13" t="n"/>
-      <c r="R7" s="14" t="n"/>
-      <c r="S7" s="15" t="n"/>
+      <c r="N7" s="34" t="n"/>
+      <c r="O7" s="35" t="n"/>
+      <c r="P7" s="36" t="n"/>
+      <c r="Q7" s="34" t="n"/>
+      <c r="R7" s="35" t="n"/>
+      <c r="S7" s="36" t="n"/>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -984,24 +1098,24 @@
           <t>3 樓</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="15" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="15" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="14" t="n"/>
-      <c r="P8" s="15" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="14" t="n"/>
-      <c r="S8" s="15" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="34" t="n"/>
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="35" t="n"/>
+      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="34" t="n"/>
+      <c r="L8" s="35" t="n"/>
+      <c r="M8" s="36" t="n"/>
+      <c r="N8" s="34" t="n"/>
+      <c r="O8" s="35" t="n"/>
+      <c r="P8" s="36" t="n"/>
+      <c r="Q8" s="34" t="n"/>
+      <c r="R8" s="35" t="n"/>
+      <c r="S8" s="36" t="n"/>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -1009,24 +1123,24 @@
           <t>4 樓</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="15" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="15" t="n"/>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="15" t="n"/>
-      <c r="Q9" s="13" t="n"/>
-      <c r="R9" s="14" t="n"/>
-      <c r="S9" s="15" t="n"/>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="35" t="n"/>
+      <c r="J9" s="36" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="35" t="n"/>
+      <c r="M9" s="36" t="n"/>
+      <c r="N9" s="34" t="n"/>
+      <c r="O9" s="35" t="n"/>
+      <c r="P9" s="36" t="n"/>
+      <c r="Q9" s="34" t="n"/>
+      <c r="R9" s="35" t="n"/>
+      <c r="S9" s="36" t="n"/>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -1034,24 +1148,24 @@
           <t>5 樓</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="14" t="n"/>
-      <c r="J10" s="15" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="15" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="14" t="n"/>
-      <c r="P10" s="15" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="14" t="n"/>
-      <c r="S10" s="15" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="34" t="n"/>
+      <c r="I10" s="35" t="n"/>
+      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="34" t="n"/>
+      <c r="L10" s="35" t="n"/>
+      <c r="M10" s="36" t="n"/>
+      <c r="N10" s="34" t="n"/>
+      <c r="O10" s="35" t="n"/>
+      <c r="P10" s="36" t="n"/>
+      <c r="Q10" s="34" t="n"/>
+      <c r="R10" s="35" t="n"/>
+      <c r="S10" s="36" t="n"/>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -1059,24 +1173,24 @@
           <t>6 樓</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="14" t="n"/>
-      <c r="J11" s="15" t="n"/>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="15" t="n"/>
-      <c r="N11" s="13" t="n"/>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="15" t="n"/>
-      <c r="Q11" s="13" t="n"/>
-      <c r="R11" s="14" t="n"/>
-      <c r="S11" s="15" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="36" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="35" t="n"/>
+      <c r="M11" s="36" t="n"/>
+      <c r="N11" s="34" t="n"/>
+      <c r="O11" s="35" t="n"/>
+      <c r="P11" s="36" t="n"/>
+      <c r="Q11" s="34" t="n"/>
+      <c r="R11" s="35" t="n"/>
+      <c r="S11" s="36" t="n"/>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -1084,24 +1198,24 @@
           <t>7 樓</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="14" t="n"/>
-      <c r="J12" s="15" t="n"/>
-      <c r="K12" s="13" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="13" t="n"/>
-      <c r="O12" s="14" t="n"/>
-      <c r="P12" s="15" t="n"/>
-      <c r="Q12" s="13" t="n"/>
-      <c r="R12" s="14" t="n"/>
-      <c r="S12" s="15" t="n"/>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="34" t="n"/>
+      <c r="I12" s="35" t="n"/>
+      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="34" t="n"/>
+      <c r="L12" s="35" t="n"/>
+      <c r="M12" s="36" t="n"/>
+      <c r="N12" s="34" t="n"/>
+      <c r="O12" s="35" t="n"/>
+      <c r="P12" s="36" t="n"/>
+      <c r="Q12" s="34" t="n"/>
+      <c r="R12" s="35" t="n"/>
+      <c r="S12" s="36" t="n"/>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -1109,24 +1223,24 @@
           <t>8 樓</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="14" t="n"/>
-      <c r="J13" s="15" t="n"/>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="15" t="n"/>
-      <c r="N13" s="13" t="n"/>
-      <c r="O13" s="14" t="n"/>
-      <c r="P13" s="15" t="n"/>
-      <c r="Q13" s="13" t="n"/>
-      <c r="R13" s="14" t="n"/>
-      <c r="S13" s="15" t="n"/>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="34" t="n"/>
+      <c r="I13" s="35" t="n"/>
+      <c r="J13" s="36" t="n"/>
+      <c r="K13" s="34" t="n"/>
+      <c r="L13" s="35" t="n"/>
+      <c r="M13" s="36" t="n"/>
+      <c r="N13" s="34" t="n"/>
+      <c r="O13" s="35" t="n"/>
+      <c r="P13" s="36" t="n"/>
+      <c r="Q13" s="34" t="n"/>
+      <c r="R13" s="35" t="n"/>
+      <c r="S13" s="36" t="n"/>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -1134,24 +1248,24 @@
           <t>9 樓</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="15" t="n"/>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="14" t="n"/>
-      <c r="M14" s="15" t="n"/>
-      <c r="N14" s="13" t="n"/>
-      <c r="O14" s="14" t="n"/>
-      <c r="P14" s="15" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="14" t="n"/>
-      <c r="S14" s="15" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="34" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="34" t="n"/>
+      <c r="L14" s="35" t="n"/>
+      <c r="M14" s="36" t="n"/>
+      <c r="N14" s="34" t="n"/>
+      <c r="O14" s="35" t="n"/>
+      <c r="P14" s="36" t="n"/>
+      <c r="Q14" s="34" t="n"/>
+      <c r="R14" s="35" t="n"/>
+      <c r="S14" s="36" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -1159,24 +1273,24 @@
           <t>10 樓</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="14" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="15" t="n"/>
-      <c r="N15" s="13" t="n"/>
-      <c r="O15" s="14" t="n"/>
-      <c r="P15" s="15" t="n"/>
-      <c r="Q15" s="13" t="n"/>
-      <c r="R15" s="14" t="n"/>
-      <c r="S15" s="15" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="35" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="34" t="n"/>
+      <c r="L15" s="35" t="n"/>
+      <c r="M15" s="36" t="n"/>
+      <c r="N15" s="34" t="n"/>
+      <c r="O15" s="35" t="n"/>
+      <c r="P15" s="36" t="n"/>
+      <c r="Q15" s="34" t="n"/>
+      <c r="R15" s="35" t="n"/>
+      <c r="S15" s="36" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -1184,24 +1298,24 @@
           <t>11 樓</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="14" t="n"/>
-      <c r="S16" s="15" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="34" t="n"/>
+      <c r="L16" s="35" t="n"/>
+      <c r="M16" s="36" t="n"/>
+      <c r="N16" s="34" t="n"/>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="36" t="n"/>
+      <c r="Q16" s="34" t="n"/>
+      <c r="R16" s="35" t="n"/>
+      <c r="S16" s="36" t="n"/>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -1209,24 +1323,24 @@
           <t>12 樓</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="15" t="n"/>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="13" t="n"/>
-      <c r="R17" s="14" t="n"/>
-      <c r="S17" s="15" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="34" t="n"/>
+      <c r="I17" s="35" t="n"/>
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="34" t="n"/>
+      <c r="L17" s="35" t="n"/>
+      <c r="M17" s="36" t="n"/>
+      <c r="N17" s="34" t="n"/>
+      <c r="O17" s="35" t="n"/>
+      <c r="P17" s="36" t="n"/>
+      <c r="Q17" s="34" t="n"/>
+      <c r="R17" s="35" t="n"/>
+      <c r="S17" s="36" t="n"/>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -1234,24 +1348,24 @@
           <t>13 樓</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="14" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="13" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="13" t="n"/>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="13" t="n"/>
-      <c r="R18" s="14" t="n"/>
-      <c r="S18" s="15" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="34" t="n"/>
+      <c r="I18" s="35" t="n"/>
+      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="34" t="n"/>
+      <c r="L18" s="35" t="n"/>
+      <c r="M18" s="36" t="n"/>
+      <c r="N18" s="34" t="n"/>
+      <c r="O18" s="35" t="n"/>
+      <c r="P18" s="36" t="n"/>
+      <c r="Q18" s="34" t="n"/>
+      <c r="R18" s="35" t="n"/>
+      <c r="S18" s="36" t="n"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -1259,24 +1373,24 @@
           <t>14 樓</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="14" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="13" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="13" t="n"/>
-      <c r="R19" s="14" t="n"/>
-      <c r="S19" s="15" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="34" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="34" t="n"/>
+      <c r="I19" s="35" t="n"/>
+      <c r="J19" s="36" t="n"/>
+      <c r="K19" s="34" t="n"/>
+      <c r="L19" s="35" t="n"/>
+      <c r="M19" s="36" t="n"/>
+      <c r="N19" s="34" t="n"/>
+      <c r="O19" s="35" t="n"/>
+      <c r="P19" s="36" t="n"/>
+      <c r="Q19" s="34" t="n"/>
+      <c r="R19" s="35" t="n"/>
+      <c r="S19" s="36" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -1284,24 +1398,24 @@
           <t>15 樓</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="13" t="n"/>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="14" t="n"/>
-      <c r="S20" s="15" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="34" t="n"/>
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="34" t="n"/>
+      <c r="L20" s="35" t="n"/>
+      <c r="M20" s="36" t="n"/>
+      <c r="N20" s="34" t="n"/>
+      <c r="O20" s="35" t="n"/>
+      <c r="P20" s="36" t="n"/>
+      <c r="Q20" s="34" t="n"/>
+      <c r="R20" s="35" t="n"/>
+      <c r="S20" s="36" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -1309,24 +1423,24 @@
           <t>16 樓</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="14" t="n"/>
-      <c r="J21" s="15" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="15" t="n"/>
-      <c r="N21" s="13" t="n"/>
-      <c r="O21" s="14" t="n"/>
-      <c r="P21" s="15" t="n"/>
-      <c r="Q21" s="13" t="n"/>
-      <c r="R21" s="14" t="n"/>
-      <c r="S21" s="15" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="34" t="n"/>
+      <c r="I21" s="35" t="n"/>
+      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="34" t="n"/>
+      <c r="L21" s="35" t="n"/>
+      <c r="M21" s="36" t="n"/>
+      <c r="N21" s="34" t="n"/>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="36" t="n"/>
+      <c r="Q21" s="34" t="n"/>
+      <c r="R21" s="35" t="n"/>
+      <c r="S21" s="36" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -1334,24 +1448,24 @@
           <t>17 樓</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="14" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="13" t="n"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="13" t="n"/>
-      <c r="O22" s="14" t="n"/>
-      <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-      <c r="R22" s="14" t="n"/>
-      <c r="S22" s="15" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="34" t="n"/>
+      <c r="I22" s="35" t="n"/>
+      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="34" t="n"/>
+      <c r="L22" s="35" t="n"/>
+      <c r="M22" s="36" t="n"/>
+      <c r="N22" s="34" t="n"/>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="36" t="n"/>
+      <c r="Q22" s="34" t="n"/>
+      <c r="R22" s="35" t="n"/>
+      <c r="S22" s="36" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -1359,24 +1473,24 @@
           <t>18 樓</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="14" t="n"/>
-      <c r="J23" s="15" t="n"/>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="14" t="n"/>
-      <c r="M23" s="15" t="n"/>
-      <c r="N23" s="13" t="n"/>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="15" t="n"/>
-      <c r="Q23" s="13" t="n"/>
-      <c r="R23" s="14" t="n"/>
-      <c r="S23" s="15" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="34" t="n"/>
+      <c r="I23" s="35" t="n"/>
+      <c r="J23" s="36" t="n"/>
+      <c r="K23" s="34" t="n"/>
+      <c r="L23" s="35" t="n"/>
+      <c r="M23" s="36" t="n"/>
+      <c r="N23" s="34" t="n"/>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="36" t="n"/>
+      <c r="Q23" s="34" t="n"/>
+      <c r="R23" s="35" t="n"/>
+      <c r="S23" s="36" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -1384,24 +1498,24 @@
           <t>19 樓</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="15" t="n"/>
-      <c r="K24" s="13" t="n"/>
-      <c r="L24" s="14" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="13" t="n"/>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="15" t="n"/>
-      <c r="Q24" s="13" t="n"/>
-      <c r="R24" s="14" t="n"/>
-      <c r="S24" s="15" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="35" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="34" t="n"/>
+      <c r="L24" s="35" t="n"/>
+      <c r="M24" s="36" t="n"/>
+      <c r="N24" s="34" t="n"/>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="36" t="n"/>
+      <c r="Q24" s="34" t="n"/>
+      <c r="R24" s="35" t="n"/>
+      <c r="S24" s="36" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -1409,24 +1523,24 @@
           <t>20 樓</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="15" t="n"/>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="14" t="n"/>
-      <c r="M25" s="15" t="n"/>
-      <c r="N25" s="13" t="n"/>
-      <c r="O25" s="14" t="n"/>
-      <c r="P25" s="15" t="n"/>
-      <c r="Q25" s="13" t="n"/>
-      <c r="R25" s="14" t="n"/>
-      <c r="S25" s="15" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="34" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="34" t="n"/>
+      <c r="I25" s="35" t="n"/>
+      <c r="J25" s="36" t="n"/>
+      <c r="K25" s="34" t="n"/>
+      <c r="L25" s="35" t="n"/>
+      <c r="M25" s="36" t="n"/>
+      <c r="N25" s="34" t="n"/>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="36" t="n"/>
+      <c r="Q25" s="34" t="n"/>
+      <c r="R25" s="35" t="n"/>
+      <c r="S25" s="36" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -1434,24 +1548,24 @@
           <t>21 樓</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="14" t="n"/>
-      <c r="J26" s="15" t="n"/>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="14" t="n"/>
-      <c r="M26" s="15" t="n"/>
-      <c r="N26" s="13" t="n"/>
-      <c r="O26" s="14" t="n"/>
-      <c r="P26" s="15" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="14" t="n"/>
-      <c r="S26" s="15" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="34" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="34" t="n"/>
+      <c r="I26" s="35" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="34" t="n"/>
+      <c r="L26" s="35" t="n"/>
+      <c r="M26" s="36" t="n"/>
+      <c r="N26" s="34" t="n"/>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="36" t="n"/>
+      <c r="Q26" s="34" t="n"/>
+      <c r="R26" s="35" t="n"/>
+      <c r="S26" s="36" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -1459,24 +1573,24 @@
           <t>22 樓</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="14" t="n"/>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="14" t="n"/>
-      <c r="M27" s="15" t="n"/>
-      <c r="N27" s="13" t="n"/>
-      <c r="O27" s="14" t="n"/>
-      <c r="P27" s="15" t="n"/>
-      <c r="Q27" s="13" t="n"/>
-      <c r="R27" s="14" t="n"/>
-      <c r="S27" s="15" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="34" t="n"/>
+      <c r="I27" s="35" t="n"/>
+      <c r="J27" s="36" t="n"/>
+      <c r="K27" s="34" t="n"/>
+      <c r="L27" s="35" t="n"/>
+      <c r="M27" s="36" t="n"/>
+      <c r="N27" s="34" t="n"/>
+      <c r="O27" s="35" t="n"/>
+      <c r="P27" s="36" t="n"/>
+      <c r="Q27" s="34" t="n"/>
+      <c r="R27" s="35" t="n"/>
+      <c r="S27" s="36" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -1484,24 +1598,24 @@
           <t>23 樓</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="14" t="n"/>
-      <c r="J28" s="15" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="14" t="n"/>
-      <c r="M28" s="15" t="n"/>
-      <c r="N28" s="13" t="n"/>
-      <c r="O28" s="14" t="n"/>
-      <c r="P28" s="15" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="14" t="n"/>
-      <c r="S28" s="15" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="34" t="n"/>
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="34" t="n"/>
+      <c r="I28" s="35" t="n"/>
+      <c r="J28" s="36" t="n"/>
+      <c r="K28" s="34" t="n"/>
+      <c r="L28" s="35" t="n"/>
+      <c r="M28" s="36" t="n"/>
+      <c r="N28" s="34" t="n"/>
+      <c r="O28" s="35" t="n"/>
+      <c r="P28" s="36" t="n"/>
+      <c r="Q28" s="34" t="n"/>
+      <c r="R28" s="35" t="n"/>
+      <c r="S28" s="36" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -1509,24 +1623,24 @@
           <t>24 樓</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="14" t="n"/>
-      <c r="J29" s="15" t="n"/>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="14" t="n"/>
-      <c r="M29" s="15" t="n"/>
-      <c r="N29" s="13" t="n"/>
-      <c r="O29" s="14" t="n"/>
-      <c r="P29" s="15" t="n"/>
-      <c r="Q29" s="13" t="n"/>
-      <c r="R29" s="14" t="n"/>
-      <c r="S29" s="15" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="35" t="n"/>
+      <c r="G29" s="36" t="n"/>
+      <c r="H29" s="34" t="n"/>
+      <c r="I29" s="35" t="n"/>
+      <c r="J29" s="36" t="n"/>
+      <c r="K29" s="34" t="n"/>
+      <c r="L29" s="35" t="n"/>
+      <c r="M29" s="36" t="n"/>
+      <c r="N29" s="34" t="n"/>
+      <c r="O29" s="35" t="n"/>
+      <c r="P29" s="36" t="n"/>
+      <c r="Q29" s="34" t="n"/>
+      <c r="R29" s="35" t="n"/>
+      <c r="S29" s="36" t="n"/>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -1534,24 +1648,24 @@
           <t>25 樓</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="15" t="n"/>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="14" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="13" t="n"/>
-      <c r="O30" s="14" t="n"/>
-      <c r="P30" s="15" t="n"/>
-      <c r="Q30" s="13" t="n"/>
-      <c r="R30" s="14" t="n"/>
-      <c r="S30" s="15" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="35" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="34" t="n"/>
+      <c r="I30" s="35" t="n"/>
+      <c r="J30" s="36" t="n"/>
+      <c r="K30" s="34" t="n"/>
+      <c r="L30" s="35" t="n"/>
+      <c r="M30" s="36" t="n"/>
+      <c r="N30" s="34" t="n"/>
+      <c r="O30" s="35" t="n"/>
+      <c r="P30" s="36" t="n"/>
+      <c r="Q30" s="34" t="n"/>
+      <c r="R30" s="35" t="n"/>
+      <c r="S30" s="36" t="n"/>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -1559,24 +1673,24 @@
           <t>26 樓</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="15" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="14" t="n"/>
-      <c r="M31" s="15" t="n"/>
-      <c r="N31" s="13" t="n"/>
-      <c r="O31" s="14" t="n"/>
-      <c r="P31" s="15" t="n"/>
-      <c r="Q31" s="13" t="n"/>
-      <c r="R31" s="14" t="n"/>
-      <c r="S31" s="15" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="34" t="n"/>
+      <c r="F31" s="35" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="34" t="n"/>
+      <c r="I31" s="35" t="n"/>
+      <c r="J31" s="36" t="n"/>
+      <c r="K31" s="34" t="n"/>
+      <c r="L31" s="35" t="n"/>
+      <c r="M31" s="36" t="n"/>
+      <c r="N31" s="34" t="n"/>
+      <c r="O31" s="35" t="n"/>
+      <c r="P31" s="36" t="n"/>
+      <c r="Q31" s="34" t="n"/>
+      <c r="R31" s="35" t="n"/>
+      <c r="S31" s="36" t="n"/>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
@@ -1584,24 +1698,24 @@
           <t>27 樓</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="15" t="n"/>
-      <c r="K32" s="13" t="n"/>
-      <c r="L32" s="14" t="n"/>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="13" t="n"/>
-      <c r="O32" s="14" t="n"/>
-      <c r="P32" s="15" t="n"/>
-      <c r="Q32" s="13" t="n"/>
-      <c r="R32" s="14" t="n"/>
-      <c r="S32" s="15" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="34" t="n"/>
+      <c r="F32" s="35" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="34" t="n"/>
+      <c r="I32" s="35" t="n"/>
+      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="34" t="n"/>
+      <c r="L32" s="35" t="n"/>
+      <c r="M32" s="36" t="n"/>
+      <c r="N32" s="34" t="n"/>
+      <c r="O32" s="35" t="n"/>
+      <c r="P32" s="36" t="n"/>
+      <c r="Q32" s="34" t="n"/>
+      <c r="R32" s="35" t="n"/>
+      <c r="S32" s="36" t="n"/>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -1609,24 +1723,24 @@
           <t>28 樓</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="15" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="15" t="n"/>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="14" t="n"/>
-      <c r="M33" s="15" t="n"/>
-      <c r="N33" s="13" t="n"/>
-      <c r="O33" s="14" t="n"/>
-      <c r="P33" s="15" t="n"/>
-      <c r="Q33" s="13" t="n"/>
-      <c r="R33" s="14" t="n"/>
-      <c r="S33" s="15" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="34" t="n"/>
+      <c r="F33" s="35" t="n"/>
+      <c r="G33" s="36" t="n"/>
+      <c r="H33" s="34" t="n"/>
+      <c r="I33" s="35" t="n"/>
+      <c r="J33" s="36" t="n"/>
+      <c r="K33" s="34" t="n"/>
+      <c r="L33" s="35" t="n"/>
+      <c r="M33" s="36" t="n"/>
+      <c r="N33" s="34" t="n"/>
+      <c r="O33" s="35" t="n"/>
+      <c r="P33" s="36" t="n"/>
+      <c r="Q33" s="34" t="n"/>
+      <c r="R33" s="35" t="n"/>
+      <c r="S33" s="36" t="n"/>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -1634,24 +1748,24 @@
           <t>29 樓</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="15" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="14" t="n"/>
-      <c r="J34" s="15" t="n"/>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="14" t="n"/>
-      <c r="M34" s="15" t="n"/>
-      <c r="N34" s="13" t="n"/>
-      <c r="O34" s="14" t="n"/>
-      <c r="P34" s="15" t="n"/>
-      <c r="Q34" s="13" t="n"/>
-      <c r="R34" s="14" t="n"/>
-      <c r="S34" s="15" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="34" t="n"/>
+      <c r="F34" s="35" t="n"/>
+      <c r="G34" s="36" t="n"/>
+      <c r="H34" s="34" t="n"/>
+      <c r="I34" s="35" t="n"/>
+      <c r="J34" s="36" t="n"/>
+      <c r="K34" s="34" t="n"/>
+      <c r="L34" s="35" t="n"/>
+      <c r="M34" s="36" t="n"/>
+      <c r="N34" s="34" t="n"/>
+      <c r="O34" s="35" t="n"/>
+      <c r="P34" s="36" t="n"/>
+      <c r="Q34" s="34" t="n"/>
+      <c r="R34" s="35" t="n"/>
+      <c r="S34" s="36" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -1659,24 +1773,24 @@
           <t>30 樓</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="15" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="14" t="n"/>
-      <c r="J35" s="15" t="n"/>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="14" t="n"/>
-      <c r="M35" s="15" t="n"/>
-      <c r="N35" s="13" t="n"/>
-      <c r="O35" s="14" t="n"/>
-      <c r="P35" s="15" t="n"/>
-      <c r="Q35" s="13" t="n"/>
-      <c r="R35" s="14" t="n"/>
-      <c r="S35" s="15" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="34" t="n"/>
+      <c r="F35" s="35" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="34" t="n"/>
+      <c r="I35" s="35" t="n"/>
+      <c r="J35" s="36" t="n"/>
+      <c r="K35" s="34" t="n"/>
+      <c r="L35" s="35" t="n"/>
+      <c r="M35" s="36" t="n"/>
+      <c r="N35" s="34" t="n"/>
+      <c r="O35" s="35" t="n"/>
+      <c r="P35" s="36" t="n"/>
+      <c r="Q35" s="34" t="n"/>
+      <c r="R35" s="35" t="n"/>
+      <c r="S35" s="36" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
@@ -1684,24 +1798,24 @@
           <t>31 樓</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="14" t="n"/>
-      <c r="J36" s="15" t="n"/>
-      <c r="K36" s="13" t="n"/>
-      <c r="L36" s="14" t="n"/>
-      <c r="M36" s="15" t="n"/>
-      <c r="N36" s="13" t="n"/>
-      <c r="O36" s="14" t="n"/>
-      <c r="P36" s="15" t="n"/>
-      <c r="Q36" s="13" t="n"/>
-      <c r="R36" s="14" t="n"/>
-      <c r="S36" s="15" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="35" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="34" t="n"/>
+      <c r="I36" s="35" t="n"/>
+      <c r="J36" s="36" t="n"/>
+      <c r="K36" s="34" t="n"/>
+      <c r="L36" s="35" t="n"/>
+      <c r="M36" s="36" t="n"/>
+      <c r="N36" s="34" t="n"/>
+      <c r="O36" s="35" t="n"/>
+      <c r="P36" s="36" t="n"/>
+      <c r="Q36" s="34" t="n"/>
+      <c r="R36" s="35" t="n"/>
+      <c r="S36" s="36" t="n"/>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
@@ -1709,24 +1823,24 @@
           <t>32 樓</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="15" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="14" t="n"/>
-      <c r="J37" s="15" t="n"/>
-      <c r="K37" s="13" t="n"/>
-      <c r="L37" s="14" t="n"/>
-      <c r="M37" s="15" t="n"/>
-      <c r="N37" s="13" t="n"/>
-      <c r="O37" s="14" t="n"/>
-      <c r="P37" s="15" t="n"/>
-      <c r="Q37" s="13" t="n"/>
-      <c r="R37" s="14" t="n"/>
-      <c r="S37" s="15" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="34" t="n"/>
+      <c r="F37" s="35" t="n"/>
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="34" t="n"/>
+      <c r="I37" s="35" t="n"/>
+      <c r="J37" s="36" t="n"/>
+      <c r="K37" s="34" t="n"/>
+      <c r="L37" s="35" t="n"/>
+      <c r="M37" s="36" t="n"/>
+      <c r="N37" s="34" t="n"/>
+      <c r="O37" s="35" t="n"/>
+      <c r="P37" s="36" t="n"/>
+      <c r="Q37" s="34" t="n"/>
+      <c r="R37" s="35" t="n"/>
+      <c r="S37" s="36" t="n"/>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
@@ -1734,24 +1848,24 @@
           <t>33 樓</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="15" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="14" t="n"/>
-      <c r="J38" s="15" t="n"/>
-      <c r="K38" s="13" t="n"/>
-      <c r="L38" s="14" t="n"/>
-      <c r="M38" s="15" t="n"/>
-      <c r="N38" s="13" t="n"/>
-      <c r="O38" s="14" t="n"/>
-      <c r="P38" s="15" t="n"/>
-      <c r="Q38" s="13" t="n"/>
-      <c r="R38" s="14" t="n"/>
-      <c r="S38" s="15" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="34" t="n"/>
+      <c r="F38" s="35" t="n"/>
+      <c r="G38" s="36" t="n"/>
+      <c r="H38" s="34" t="n"/>
+      <c r="I38" s="35" t="n"/>
+      <c r="J38" s="36" t="n"/>
+      <c r="K38" s="34" t="n"/>
+      <c r="L38" s="35" t="n"/>
+      <c r="M38" s="36" t="n"/>
+      <c r="N38" s="34" t="n"/>
+      <c r="O38" s="35" t="n"/>
+      <c r="P38" s="36" t="n"/>
+      <c r="Q38" s="34" t="n"/>
+      <c r="R38" s="35" t="n"/>
+      <c r="S38" s="36" t="n"/>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
@@ -1759,24 +1873,24 @@
           <t>34 樓</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="14" t="n"/>
-      <c r="G39" s="15" t="n"/>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="14" t="n"/>
-      <c r="J39" s="15" t="n"/>
-      <c r="K39" s="13" t="n"/>
-      <c r="L39" s="14" t="n"/>
-      <c r="M39" s="15" t="n"/>
-      <c r="N39" s="13" t="n"/>
-      <c r="O39" s="14" t="n"/>
-      <c r="P39" s="15" t="n"/>
-      <c r="Q39" s="13" t="n"/>
-      <c r="R39" s="14" t="n"/>
-      <c r="S39" s="15" t="n"/>
+      <c r="B39" s="34" t="n"/>
+      <c r="C39" s="35" t="n"/>
+      <c r="D39" s="36" t="n"/>
+      <c r="E39" s="34" t="n"/>
+      <c r="F39" s="35" t="n"/>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="34" t="n"/>
+      <c r="I39" s="35" t="n"/>
+      <c r="J39" s="36" t="n"/>
+      <c r="K39" s="34" t="n"/>
+      <c r="L39" s="35" t="n"/>
+      <c r="M39" s="36" t="n"/>
+      <c r="N39" s="34" t="n"/>
+      <c r="O39" s="35" t="n"/>
+      <c r="P39" s="36" t="n"/>
+      <c r="Q39" s="34" t="n"/>
+      <c r="R39" s="35" t="n"/>
+      <c r="S39" s="36" t="n"/>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
@@ -1784,25 +1898,27 @@
           <t>35 樓</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n"/>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="21" t="n"/>
-      <c r="G40" s="22" t="n"/>
-      <c r="H40" s="20" t="n"/>
-      <c r="I40" s="21" t="n"/>
-      <c r="J40" s="22" t="n"/>
-      <c r="K40" s="20" t="n"/>
-      <c r="L40" s="21" t="n"/>
-      <c r="M40" s="22" t="n"/>
-      <c r="N40" s="20" t="n"/>
-      <c r="O40" s="21" t="n"/>
-      <c r="P40" s="22" t="n"/>
-      <c r="Q40" s="20" t="n"/>
-      <c r="R40" s="21" t="n"/>
-      <c r="S40" s="22" t="n"/>
-    </row>
+      <c r="B40" s="40" t="n"/>
+      <c r="C40" s="41" t="n"/>
+      <c r="D40" s="42" t="n"/>
+      <c r="E40" s="40" t="n"/>
+      <c r="F40" s="41" t="n"/>
+      <c r="G40" s="42" t="n"/>
+      <c r="H40" s="40" t="n"/>
+      <c r="I40" s="41" t="n"/>
+      <c r="J40" s="42" t="n"/>
+      <c r="K40" s="40" t="n"/>
+      <c r="L40" s="41" t="n"/>
+      <c r="M40" s="42" t="n"/>
+      <c r="N40" s="40" t="n"/>
+      <c r="O40" s="41" t="n"/>
+      <c r="P40" s="42" t="n"/>
+      <c r="Q40" s="40" t="n"/>
+      <c r="R40" s="41" t="n"/>
+      <c r="S40" s="42" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
@@ -1845,6 +1961,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -1948,7 +2065,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1962,10 +2079,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2004,6 +2121,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
@@ -2037,10 +2155,10 @@
           <t>2 樓</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="43" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -2048,10 +2166,10 @@
           <t>3 樓</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="43" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -2059,10 +2177,10 @@
           <t>4 樓</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="43" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -2070,10 +2188,10 @@
           <t>5 樓</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="28" t="n"/>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="43" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -2081,10 +2199,10 @@
           <t>6 樓</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="28" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="43" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -2092,10 +2210,10 @@
           <t>7 樓</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="28" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="43" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -2103,10 +2221,10 @@
           <t>8 樓</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="28" t="n"/>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="43" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -2114,10 +2232,10 @@
           <t>9 樓</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="28" t="n"/>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="43" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -2125,10 +2243,10 @@
           <t>10 樓</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="28" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="43" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -2136,10 +2254,10 @@
           <t>11 樓</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="28" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="43" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -2147,10 +2265,10 @@
           <t>12 樓</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="28" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="43" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -2158,10 +2276,10 @@
           <t>13 樓</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="28" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="43" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -2169,10 +2287,10 @@
           <t>14 樓</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="28" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="43" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -2180,10 +2298,10 @@
           <t>15 樓</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="28" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="43" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -2191,10 +2309,10 @@
           <t>16 樓</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="28" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="43" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -2202,10 +2320,10 @@
           <t>17 樓</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="28" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="43" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -2213,10 +2331,10 @@
           <t>18 樓</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="28" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="43" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -2224,10 +2342,10 @@
           <t>19 樓</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="28" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="43" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -2235,10 +2353,10 @@
           <t>20 樓</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="28" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="43" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -2246,10 +2364,10 @@
           <t>21 樓</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="28" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="43" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -2257,10 +2375,10 @@
           <t>22 樓</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="28" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="43" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -2268,10 +2386,10 @@
           <t>23 樓</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="28" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="43" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -2279,10 +2397,10 @@
           <t>24 樓</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="28" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="43" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -2290,10 +2408,10 @@
           <t>25 樓</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="28" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="43" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -2301,10 +2419,10 @@
           <t>26 樓</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="28" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="43" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -2312,10 +2430,10 @@
           <t>27 樓</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="28" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="43" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
@@ -2323,10 +2441,10 @@
           <t>28 樓</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="28" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="43" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -2334,10 +2452,10 @@
           <t>29 樓</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="28" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="43" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -2345,10 +2463,10 @@
           <t>30 樓</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="28" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="43" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -2356,10 +2474,10 @@
           <t>31 樓</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="28" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="43" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
@@ -2367,10 +2485,10 @@
           <t>32 樓</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="28" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="43" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
@@ -2378,10 +2496,10 @@
           <t>33 樓</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="28" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="43" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
@@ -2389,10 +2507,10 @@
           <t>34 樓</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="28" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="43" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -2400,11 +2518,12 @@
           <t>35 樓</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-    </row>
+      <c r="B39" s="40" t="n"/>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="44" t="n"/>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
@@ -2415,7 +2534,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2429,10 +2548,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2471,6 +2590,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
@@ -2504,10 +2624,10 @@
           <t>2 樓</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="43" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -2515,10 +2635,10 @@
           <t>3 樓</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="43" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -2526,10 +2646,10 @@
           <t>4 樓</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="43" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -2537,10 +2657,10 @@
           <t>5 樓</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="28" t="n"/>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="43" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -2548,10 +2668,10 @@
           <t>6 樓</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="28" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="43" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -2559,10 +2679,10 @@
           <t>7 樓</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="28" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="43" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -2570,10 +2690,10 @@
           <t>8 樓</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="28" t="n"/>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="43" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -2581,10 +2701,10 @@
           <t>9 樓</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="28" t="n"/>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="43" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -2592,10 +2712,10 @@
           <t>10 樓</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="28" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="43" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -2603,10 +2723,10 @@
           <t>11 樓</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="28" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="43" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -2614,10 +2734,10 @@
           <t>12 樓</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="28" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="43" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -2625,10 +2745,10 @@
           <t>13 樓</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="28" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="43" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -2636,10 +2756,10 @@
           <t>14 樓</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="28" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="43" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -2647,10 +2767,10 @@
           <t>15 樓</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="28" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="43" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -2658,10 +2778,10 @@
           <t>16 樓</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="28" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="43" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -2669,10 +2789,10 @@
           <t>17 樓</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="28" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="43" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -2680,10 +2800,10 @@
           <t>18 樓</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="28" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="43" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -2691,10 +2811,10 @@
           <t>19 樓</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="28" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="43" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -2702,10 +2822,10 @@
           <t>20 樓</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="28" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="43" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -2713,10 +2833,10 @@
           <t>21 樓</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="28" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="43" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -2724,10 +2844,10 @@
           <t>22 樓</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="28" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="43" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -2735,10 +2855,10 @@
           <t>23 樓</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="28" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="43" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -2746,10 +2866,10 @@
           <t>24 樓</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="28" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="43" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -2757,10 +2877,10 @@
           <t>25 樓</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="28" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="43" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -2768,10 +2888,10 @@
           <t>26 樓</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="28" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="43" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -2779,10 +2899,10 @@
           <t>27 樓</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="28" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="43" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
@@ -2790,10 +2910,10 @@
           <t>28 樓</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="28" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="43" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -2801,10 +2921,10 @@
           <t>29 樓</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="28" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="43" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -2812,10 +2932,10 @@
           <t>30 樓</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="28" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="43" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -2823,10 +2943,10 @@
           <t>31 樓</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="28" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="43" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
@@ -2834,10 +2954,10 @@
           <t>32 樓</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="28" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="43" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
@@ -2845,10 +2965,10 @@
           <t>33 樓</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="28" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="43" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
@@ -2856,10 +2976,10 @@
           <t>34 樓</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="28" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="43" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -2867,11 +2987,12 @@
           <t>35 樓</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-    </row>
+      <c r="B39" s="40" t="n"/>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="44" t="n"/>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
@@ -2882,7 +3003,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2896,10 +3017,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2938,6 +3059,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
@@ -2971,10 +3093,10 @@
           <t>2 樓</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="43" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -2982,10 +3104,10 @@
           <t>3 樓</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="43" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -2993,10 +3115,10 @@
           <t>4 樓</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="43" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -3004,10 +3126,10 @@
           <t>5 樓</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="28" t="n"/>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="43" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -3015,10 +3137,10 @@
           <t>6 樓</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="28" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="43" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -3026,10 +3148,10 @@
           <t>7 樓</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="28" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="43" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -3037,10 +3159,10 @@
           <t>8 樓</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="28" t="n"/>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="43" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -3048,10 +3170,10 @@
           <t>9 樓</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="28" t="n"/>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="43" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -3059,10 +3181,10 @@
           <t>10 樓</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="28" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="43" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -3070,10 +3192,10 @@
           <t>11 樓</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="28" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="43" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -3081,10 +3203,10 @@
           <t>12 樓</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="28" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="43" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -3092,10 +3214,10 @@
           <t>13 樓</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="28" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="43" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -3103,10 +3225,10 @@
           <t>14 樓</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="28" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="43" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -3114,10 +3236,10 @@
           <t>15 樓</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="28" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="43" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -3125,10 +3247,10 @@
           <t>16 樓</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="28" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="43" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -3136,10 +3258,10 @@
           <t>17 樓</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="28" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="43" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -3147,10 +3269,10 @@
           <t>18 樓</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="28" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="43" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -3158,10 +3280,10 @@
           <t>19 樓</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="28" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="43" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -3169,10 +3291,10 @@
           <t>20 樓</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="28" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="43" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -3180,10 +3302,10 @@
           <t>21 樓</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="28" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="43" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -3191,10 +3313,10 @@
           <t>22 樓</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="28" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="43" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -3202,10 +3324,10 @@
           <t>23 樓</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="28" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="43" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -3213,10 +3335,10 @@
           <t>24 樓</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="28" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="43" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -3224,10 +3346,10 @@
           <t>25 樓</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="28" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="43" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -3235,10 +3357,10 @@
           <t>26 樓</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="28" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="43" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -3246,10 +3368,10 @@
           <t>27 樓</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="28" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="43" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
@@ -3257,10 +3379,10 @@
           <t>28 樓</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="28" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="43" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -3268,10 +3390,10 @@
           <t>29 樓</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="28" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="43" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -3279,10 +3401,10 @@
           <t>30 樓</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="28" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="43" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -3290,10 +3412,10 @@
           <t>31 樓</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="28" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="43" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
@@ -3301,10 +3423,10 @@
           <t>32 樓</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="28" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="43" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
@@ -3312,10 +3434,10 @@
           <t>33 樓</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="28" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="43" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
@@ -3323,10 +3445,10 @@
           <t>34 樓</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="28" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="43" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -3334,11 +3456,12 @@
           <t>35 樓</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-    </row>
+      <c r="B39" s="40" t="n"/>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="44" t="n"/>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
@@ -3349,7 +3472,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3363,10 +3486,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3405,6 +3528,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
@@ -3438,22 +3562,22 @@
           <t>2 樓</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="28" t="n"/>
+      <c r="E6" s="43" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -3461,10 +3585,10 @@
           <t>3 樓</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="43" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -3472,10 +3596,10 @@
           <t>4 樓</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="43" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -3483,10 +3607,10 @@
           <t>5 樓</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="28" t="n"/>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="43" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -3494,10 +3618,10 @@
           <t>6 樓</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="28" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="43" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -3505,10 +3629,10 @@
           <t>7 樓</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="28" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="43" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -3516,10 +3640,10 @@
           <t>8 樓</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="28" t="n"/>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="43" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -3527,10 +3651,10 @@
           <t>9 樓</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="28" t="n"/>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="43" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -3538,10 +3662,10 @@
           <t>10 樓</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="28" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="43" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -3549,10 +3673,10 @@
           <t>11 樓</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="28" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="43" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -3560,10 +3684,10 @@
           <t>12 樓</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="28" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="43" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -3571,10 +3695,10 @@
           <t>13 樓</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="28" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="43" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -3582,10 +3706,10 @@
           <t>14 樓</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="28" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="43" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -3593,10 +3717,10 @@
           <t>15 樓</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="28" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="43" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -3604,10 +3728,10 @@
           <t>16 樓</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="28" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="43" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -3615,10 +3739,10 @@
           <t>17 樓</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="28" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="43" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -3626,10 +3750,10 @@
           <t>18 樓</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="28" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="43" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -3637,10 +3761,10 @@
           <t>19 樓</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="28" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="43" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -3648,10 +3772,10 @@
           <t>20 樓</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="28" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="43" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -3659,10 +3783,10 @@
           <t>21 樓</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="28" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="43" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -3670,10 +3794,10 @@
           <t>22 樓</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="28" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="43" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -3681,10 +3805,10 @@
           <t>23 樓</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="28" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="43" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -3692,10 +3816,10 @@
           <t>24 樓</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="28" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="43" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -3703,10 +3827,10 @@
           <t>25 樓</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="28" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="43" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -3714,10 +3838,10 @@
           <t>26 樓</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="28" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="43" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -3725,10 +3849,10 @@
           <t>27 樓</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="28" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="43" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
@@ -3736,10 +3860,10 @@
           <t>28 樓</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="28" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="43" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -3747,10 +3871,10 @@
           <t>29 樓</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="28" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="43" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -3758,10 +3882,10 @@
           <t>30 樓</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="28" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="43" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -3769,10 +3893,10 @@
           <t>31 樓</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="28" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="43" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
@@ -3780,10 +3904,10 @@
           <t>32 樓</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="28" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="43" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
@@ -3791,10 +3915,10 @@
           <t>33 樓</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="28" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="43" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
@@ -3802,10 +3926,10 @@
           <t>34 樓</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="28" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="43" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -3813,11 +3937,12 @@
           <t>35 樓</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-    </row>
+      <c r="B39" s="40" t="n"/>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="44" t="n"/>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
@@ -3835,7 +3960,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3849,10 +3974,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3891,6 +4016,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
@@ -3924,10 +4050,10 @@
           <t>2 樓</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="43" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -3935,10 +4061,10 @@
           <t>3 樓</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="43" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -3946,10 +4072,10 @@
           <t>4 樓</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="43" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -3957,10 +4083,10 @@
           <t>5 樓</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="28" t="n"/>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="43" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -3968,10 +4094,10 @@
           <t>6 樓</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="28" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="43" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -3979,10 +4105,10 @@
           <t>7 樓</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="28" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="43" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -3990,10 +4116,10 @@
           <t>8 樓</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="28" t="n"/>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="43" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -4001,10 +4127,10 @@
           <t>9 樓</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="28" t="n"/>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="43" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -4012,10 +4138,10 @@
           <t>10 樓</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="28" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="43" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -4023,10 +4149,10 @@
           <t>11 樓</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="28" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="43" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -4034,10 +4160,10 @@
           <t>12 樓</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="28" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="43" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -4045,10 +4171,10 @@
           <t>13 樓</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="28" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="43" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -4056,10 +4182,10 @@
           <t>14 樓</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="28" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="43" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -4067,10 +4193,10 @@
           <t>15 樓</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="28" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="43" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -4078,10 +4204,10 @@
           <t>16 樓</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="28" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="43" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -4089,10 +4215,10 @@
           <t>17 樓</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="28" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="43" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -4100,10 +4226,10 @@
           <t>18 樓</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="28" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="43" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -4111,10 +4237,10 @@
           <t>19 樓</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="28" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="43" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -4122,10 +4248,10 @@
           <t>20 樓</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="28" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="43" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -4133,10 +4259,10 @@
           <t>21 樓</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="28" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="43" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -4144,10 +4270,10 @@
           <t>22 樓</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="28" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="43" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -4155,10 +4281,10 @@
           <t>23 樓</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="28" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="43" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -4166,10 +4292,10 @@
           <t>24 樓</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="28" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="43" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -4177,10 +4303,10 @@
           <t>25 樓</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="28" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="43" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -4188,10 +4314,10 @@
           <t>26 樓</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="28" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="43" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -4199,10 +4325,10 @@
           <t>27 樓</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="28" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="43" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
@@ -4210,10 +4336,10 @@
           <t>28 樓</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="28" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="43" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -4221,10 +4347,10 @@
           <t>29 樓</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="28" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="43" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -4232,10 +4358,10 @@
           <t>30 樓</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="28" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="43" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -4243,10 +4369,10 @@
           <t>31 樓</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="28" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="43" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
@@ -4254,10 +4380,10 @@
           <t>32 樓</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="28" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="43" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
@@ -4265,10 +4391,10 @@
           <t>33 樓</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="28" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="43" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
@@ -4276,10 +4402,10 @@
           <t>34 樓</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="28" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="43" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -4287,11 +4413,12 @@
           <t>35 樓</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-    </row>
+      <c r="B39" s="40" t="n"/>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="44" t="n"/>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
@@ -4302,7 +4429,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4316,10 +4443,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4358,6 +4485,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
@@ -4391,10 +4519,10 @@
           <t>2 樓</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="43" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -4402,10 +4530,10 @@
           <t>3 樓</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="43" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -4413,10 +4541,10 @@
           <t>4 樓</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="43" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -4424,10 +4552,10 @@
           <t>5 樓</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="28" t="n"/>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="43" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -4435,10 +4563,10 @@
           <t>6 樓</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="28" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="43" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -4446,10 +4574,10 @@
           <t>7 樓</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="28" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="43" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -4457,10 +4585,10 @@
           <t>8 樓</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="28" t="n"/>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="43" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -4468,10 +4596,10 @@
           <t>9 樓</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="28" t="n"/>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="43" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -4479,10 +4607,10 @@
           <t>10 樓</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="28" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="43" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -4490,10 +4618,10 @@
           <t>11 樓</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="28" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="43" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -4501,10 +4629,10 @@
           <t>12 樓</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="28" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="43" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -4512,10 +4640,10 @@
           <t>13 樓</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="28" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="43" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -4523,10 +4651,10 @@
           <t>14 樓</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="28" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="43" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -4534,10 +4662,10 @@
           <t>15 樓</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="28" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="43" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -4545,10 +4673,10 @@
           <t>16 樓</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="28" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="43" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -4556,10 +4684,10 @@
           <t>17 樓</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="28" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="43" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -4567,10 +4695,10 @@
           <t>18 樓</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="28" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="43" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -4578,10 +4706,10 @@
           <t>19 樓</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="28" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="43" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -4589,10 +4717,10 @@
           <t>20 樓</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="28" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="43" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -4600,10 +4728,10 @@
           <t>21 樓</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="28" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="43" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -4611,10 +4739,10 @@
           <t>22 樓</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="28" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="43" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -4622,10 +4750,10 @@
           <t>23 樓</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="28" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="43" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -4633,10 +4761,10 @@
           <t>24 樓</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="28" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="43" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -4644,10 +4772,10 @@
           <t>25 樓</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="28" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="43" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -4655,10 +4783,10 @@
           <t>26 樓</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="28" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="43" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -4666,10 +4794,10 @@
           <t>27 樓</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="28" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="43" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
@@ -4677,10 +4805,10 @@
           <t>28 樓</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="28" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="43" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -4688,10 +4816,10 @@
           <t>29 樓</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="28" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="43" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -4699,10 +4827,10 @@
           <t>30 樓</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="28" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="43" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -4710,10 +4838,10 @@
           <t>31 樓</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="28" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="43" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
@@ -4721,10 +4849,10 @@
           <t>32 樓</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="28" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="43" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
@@ -4732,10 +4860,10 @@
           <t>33 樓</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="28" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="43" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
@@ -4743,10 +4871,10 @@
           <t>34 樓</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="28" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="43" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -4754,11 +4882,12 @@
           <t>35 樓</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-    </row>
+      <c r="B39" s="40" t="n"/>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="44" t="n"/>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
@@ -4769,6 +4898,6 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>